--- a/smoke_test/cluster_plots/cluster_means.xlsx
+++ b/smoke_test/cluster_plots/cluster_means.xlsx
@@ -732,178 +732,178 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6674972085615366</v>
+        <v>-0.5610652153507593</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4542172371475834</v>
+        <v>1.823203841201996</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05051146224079373</v>
+        <v>0.3095288783738255</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7529474759171715</v>
+        <v>-0.684396548470267</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3470555495964631</v>
+        <v>0.07327387607716442</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.41203560177454</v>
+        <v>-0.1476789106854173</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9325629522955967</v>
+        <v>-0.8511408604190521</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4110895208309274</v>
+        <v>0.7749391505118444</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2835781044929053</v>
+        <v>1.699816302177745</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2269675420052409</v>
+        <v>-0.5563802465860286</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2243172326913894</v>
+        <v>-0.9105903058624795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5932076059996668</v>
+        <v>0.8485919352268939</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1478973424602326</v>
+        <v>0.2990969892586389</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5459606780265001</v>
+        <v>-1.121579582380243</v>
       </c>
       <c r="P2" t="n">
-        <v>0.05679694356128614</v>
+        <v>0.647861577409661</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6413909292546579</v>
+        <v>-0.5629394126304296</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5650052885850987</v>
+        <v>0.2677206114582937</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5014014360192338</v>
+        <v>0.447661383401545</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9457467446920802</v>
+        <v>0.5127608476304119</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5838253852587726</v>
+        <v>0.2532923973880466</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3870272338993621</v>
+        <v>0.7013950272483042</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.9778712416965794</v>
+        <v>-1.000885071790282</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2256356305061404</v>
+        <v>-0.7430460940025754</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2183936547663865</v>
+        <v>0.480690249270275</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.8662371143279054</v>
+        <v>-0.8322815445585271</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3416940888030304</v>
+        <v>-0.4708659466034923</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1870319039000755</v>
+        <v>-0.3090419070365999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.138856023026896</v>
+        <v>0.4138882545319224</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1400971513919749</v>
+        <v>-0.4305811595520977</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1589976019369684</v>
+        <v>-0.2327792356420902</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.5893514710424989</v>
+        <v>-0.6336886716389958</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.7958028490227055</v>
+        <v>-0.81233818966842</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.5014125736347853</v>
+        <v>0.4201763964093859</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4846293790902378</v>
+        <v>0.7637411998572087</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1669733039349466</v>
+        <v>0.548998794239671</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.7859875959168441</v>
+        <v>-0.7303302345052662</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.5993814512748299</v>
+        <v>0.4533934923027168</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.102835590474976</v>
+        <v>-0.05795753353553384</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.5928489218634827</v>
+        <v>-0.9484159461163897</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.309647513013131</v>
+        <v>0.3836885331060884</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.5195442711271223</v>
+        <v>-0.6569520272358292</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.6555301788716007</v>
+        <v>-0.5996874388307195</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.6408416871715311</v>
+        <v>-0.7951034814445171</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6623496986002722</v>
+        <v>0.6688882994012668</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.278294423832236</v>
+        <v>0.7415017235474595</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3795605735157846</v>
+        <v>-0.4954211739023118</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5170758780379663</v>
+        <v>0.692510009345036</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.5900632881906597</v>
+        <v>-0.5272369985026008</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5967972303852868</v>
+        <v>0.4240745713556734</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.915764099076022</v>
+        <v>0.6473528597991157</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.404051516903855</v>
+        <v>-0.562583484317678</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.1867088317160842</v>
+        <v>0.4805589621600851</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7938693518478326</v>
+        <v>0.7804097662461916</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.6240907258190029</v>
+        <v>-0.577441226803278</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.6213357007961053</v>
+        <v>0.3249458544343475</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1282122015398305</v>
+        <v>0.3450508154096711</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.6089370957492849</v>
+        <v>-0.5612753718707644</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.4298432654419101</v>
+        <v>0.521609503474033</v>
       </c>
     </row>
     <row r="3">
@@ -913,178 +913,178 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4814994323859828</v>
+        <v>0.1312297407131234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4804300348451455</v>
+        <v>1.272763483361733</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5022191681046921</v>
+        <v>-0.1612105383304824</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5674339340396367</v>
+        <v>0.04221705949489016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08239156070250564</v>
+        <v>0.1598689291843814</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7746790178714599</v>
+        <v>-0.5415449757443792</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.76898210097203</v>
+        <v>-0.1389927156301776</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5715156529115309</v>
+        <v>0.7009627012009489</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3402774800080811</v>
+        <v>1.730373122736462</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.225121497702588</v>
+        <v>-0.7037245158822684</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.024904583549342</v>
+        <v>-0.704910919118841</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7508066437931484</v>
+        <v>0.4444774047236142</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4783221033551963</v>
+        <v>-0.3774273512177135</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.110854598908885</v>
+        <v>-1.008783724457874</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7355766845446012</v>
+        <v>-0.07528104201485336</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4656353258687542</v>
+        <v>0.08901732700595093</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1908937917772919</v>
+        <v>-0.8866794061046253</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4643390944203188</v>
+        <v>0.1215948906064154</v>
       </c>
       <c r="T3" t="n">
-        <v>0.970218838954187</v>
+        <v>0.5417897681124778</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008601377782872944</v>
+        <v>-0.7008071828619076</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5262492498147354</v>
+        <v>0.218424267140792</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9171330040396785</v>
+        <v>-0.2608779977249736</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9578091318293285</v>
+        <v>-0.9219501244043595</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2820889610802574</v>
+        <v>0.04602774055139919</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7259883639790707</v>
+        <v>-0.08334750945918884</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.054489486010781</v>
+        <v>0.268326991763199</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.5876790906316867</v>
+        <v>-0.3713386897666822</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1430501926059705</v>
+        <v>-0.3513686354784074</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7903800554285688</v>
+        <v>0.7310416184934468</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3488255060877063</v>
+        <v>-0.4317007445657867</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.5261470005270332</v>
+        <v>0.06743324278239531</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.7879101121744404</v>
+        <v>-0.1188088400162185</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6867108100147754</v>
+        <v>0.1989066385340636</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7907694464148083</v>
+        <v>-0.5305028245048599</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.6032678477956096</v>
+        <v>0.4687173744091611</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.625759301606807</v>
+        <v>-0.02623222676059956</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8353553197693262</v>
+        <v>0.8068940576472163</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1183848820100821</v>
+        <v>-0.1957634652250998</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1.139507297651111</v>
+        <v>-0.7524789193922914</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6666190791781331</v>
+        <v>-1.674676919226094</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.5016387748631806</v>
+        <v>-0.4201907321518675</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.49128755596227</v>
+        <v>0.1322048388720322</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.8284766786452487</v>
+        <v>-0.8245708148463832</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.8854761907419173</v>
+        <v>0.208003980171577</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3895322227326203</v>
+        <v>1.240047651230436</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.03218443891963699</v>
+        <v>0.3977590390173866</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3526513612640244</v>
+        <v>0.6416999470571852</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.4660421897494251</v>
+        <v>-0.03044205596511982</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5172295991378408</v>
+        <v>0.4212123400127574</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.7117522113659946</v>
+        <v>0.07019386762912586</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.6114420458324404</v>
+        <v>-0.6060828908498368</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.8085250411792138</v>
+        <v>-0.3411200212536839</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.244475724875737</v>
+        <v>0.5070817547330412</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.4530033140100235</v>
+        <v>0.1777793805168197</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.9048002164948269</v>
+        <v>0.07181465941406145</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.7095033789809417</v>
+        <v>0.4095901806452579</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.4391977571596267</v>
+        <v>0.2046977815782222</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.9316039046056375</v>
+        <v>0.4110592548861058</v>
       </c>
     </row>
     <row r="4">
@@ -1094,178 +1094,178 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8580958656469411</v>
+        <v>0.9266511442390273</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3855786033015079</v>
+        <v>0.471957274075036</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6748182016182908</v>
+        <v>-0.682455425171497</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7914465533303535</v>
+        <v>0.8609980533056217</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9132859703204733</v>
+        <v>0.8808663349212905</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1679579320054161</v>
+        <v>-0.2183070436124576</v>
       </c>
       <c r="H4" t="n">
-        <v>0.654859802532242</v>
+        <v>0.7271634311739988</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1594586676801093</v>
+        <v>-0.1572292574544529</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4693063801107976</v>
+        <v>0.4978341266030483</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6316848832093804</v>
+        <v>0.554825347901664</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05659948891727537</v>
+        <v>0.1060819223174812</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7753351794602704</v>
+        <v>-0.7836193009667901</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07055416395190507</v>
+        <v>-0.07012559082812124</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01241235652199785</v>
+        <v>0.2053213830549531</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005822047779128534</v>
+        <v>-0.1101264005040132</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8098478299368859</v>
+        <v>0.8822185869768775</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.8263709679671356</v>
+        <v>-0.7789377356044122</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.022795782154095</v>
+        <v>-1.08417933391993</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4322118656094494</v>
+        <v>-0.4341361071674796</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8298915908521226</v>
+        <v>-0.8760770358488811</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9811145551938243</v>
+        <v>-1.052262803539316</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6158812963639172</v>
+        <v>0.7050118569609469</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5850817984753302</v>
+        <v>-0.5609560634063256</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.7476933342715779</v>
+        <v>-0.7844680010747207</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.7072512087083368</v>
+        <v>0.7789919005228495</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.831967381979779</v>
+        <v>1.757839943474462</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1891653640362192</v>
+        <v>0.0663209203541051</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.7863776688893159</v>
+        <v>-0.8671738460870108</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1110260471761105</v>
+        <v>0.124830007251101</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.8531517225308914</v>
+        <v>-0.9056625718594113</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.8093393721806689</v>
+        <v>0.8773106788095768</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.6071039626994263</v>
+        <v>0.6762836726961117</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.9144039825745005</v>
+        <v>-0.9754019229403649</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.04591427376059</v>
+        <v>-1.105247879673813</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6636412824346691</v>
+        <v>0.5461934968365305</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7345643236710266</v>
+        <v>0.8050550429125383</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.481275319120185</v>
+        <v>-0.5316589845687911</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1185682473396489</v>
+        <v>0.03265230855549943</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02881231699552072</v>
+        <v>-0.004090558283541558</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.9122991264339297</v>
+        <v>-0.8693623621863183</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.2179042650109764</v>
+        <v>-0.1637511023534523</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8610615851441266</v>
+        <v>0.9302160740848817</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.3510804921162836</v>
+        <v>-0.3719184579953478</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.7306598544646694</v>
+        <v>-0.8255546643674966</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.06623589334998814</v>
+        <v>0.02107199720170395</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.6540178840085749</v>
+        <v>0.664191799955077</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.6154525887262217</v>
+        <v>-0.7013962016267949</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.7345558769505357</v>
+        <v>0.8011742457559641</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.705398538223503</v>
+        <v>-0.7960404796568389</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.3401478485380096</v>
+        <v>0.2355353821247191</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.03926059263595556</v>
+        <v>0.003693265488099639</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.8219471570054473</v>
+        <v>-0.8137964216495793</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.9165459406729298</v>
+        <v>-0.9033472514099848</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.8920518335681596</v>
+        <v>0.9589117166887345</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.8299642279484252</v>
+        <v>-0.875583829017103</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.2061692477586385</v>
+        <v>-0.2793955818433146</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.9110288780620316</v>
+        <v>0.9785469309013406</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.4240001601670323</v>
+        <v>-0.5189447508094018</v>
       </c>
     </row>
     <row r="5">
@@ -1275,178 +1275,178 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.16572969481651</v>
+        <v>-0.6020631123660883</v>
       </c>
       <c r="C5" t="n">
-        <v>1.160445465733429</v>
+        <v>-0.149279738502917</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1593110981009212</v>
+        <v>0.4604240903276892</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0782706436645136</v>
+        <v>-0.6881035386880934</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1310737496938064</v>
+        <v>-0.03257817516694329</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5064572527804276</v>
+        <v>-1.108410074864771</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1060931020075943</v>
+        <v>-0.8643012484951482</v>
       </c>
       <c r="I5" t="n">
-        <v>0.545147734404275</v>
+        <v>0.6144299075715656</v>
       </c>
       <c r="J5" t="n">
-        <v>1.578289122459762</v>
+        <v>-0.2198805908311965</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7059486328942444</v>
+        <v>-1.112319551422336</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7832728722230139</v>
+        <v>-0.6358723559843122</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3561444112678355</v>
+        <v>0.8860364328973117</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1019855533937114</v>
+        <v>-0.6224987920044199</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.041621093131594</v>
+        <v>-0.813400394745498</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.090711720457243</v>
+        <v>0.122328340367722</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.121849812209181</v>
+        <v>-0.5342175334474888</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.058468897127615</v>
+        <v>0.07676479807389597</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08827290217697555</v>
+        <v>0.7269762791647937</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6536820912805568</v>
+        <v>1.212009890030473</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7937164315190117</v>
+        <v>0.1529444933765293</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1930263855670741</v>
+        <v>0.6239661248029736</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2303171145013089</v>
+        <v>-0.9465413999118719</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.935239477341459</v>
+        <v>-0.2865669060513439</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0374000281604845</v>
+        <v>0.4358995377588494</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.05264807262401591</v>
+        <v>-0.8203619571861229</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2653653848333202</v>
+        <v>-1.212297982320209</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.3610820228093246</v>
+        <v>-0.4501543686853948</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4006251163814005</v>
+        <v>0.496000472566441</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5493445684046274</v>
+        <v>0.005700077022380877</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.4214138019613022</v>
+        <v>-0.1011263015595805</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1000537726261022</v>
+        <v>-0.4723990423070933</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1062325588217151</v>
+        <v>-0.7832312222916272</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2038867112212186</v>
+        <v>0.8676922494039692</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.6285359694889671</v>
+        <v>0.5143283496547332</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5426244457359307</v>
+        <v>-0.0671300806693714</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.007099553297277838</v>
+        <v>-0.7059712223891631</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8221324743082185</v>
+        <v>1.070293757263623</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.1337610099940353</v>
+        <v>0.4192039024480396</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.7583342704552798</v>
+        <v>-0.9903535357049795</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1.628407219448345</v>
+        <v>0.4797618637233198</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.4198409656514486</v>
+        <v>-0.3908843121289969</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.1676180593168388</v>
+        <v>-0.5866084083439402</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.7950090718349548</v>
+        <v>-0.7110480704739378</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.255230141134288</v>
+        <v>0.899007604985805</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.154279255100951</v>
+        <v>1.147765391570223</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3597412328540046</v>
+        <v>0.1348866739067836</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.6248490999029414</v>
+        <v>0.6592099263824015</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.002573751343754979</v>
+        <v>-0.5334948004513125</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.416247496674067</v>
+        <v>0.8062738786557693</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.05271338972814427</v>
+        <v>-0.3267547311279486</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.4874159769387281</v>
+        <v>-0.2967686417166918</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.3357837777505004</v>
+        <v>0.6534533168493863</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.4328568050572418</v>
+        <v>1.182389185339042</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.2146613827188962</v>
+        <v>-0.5630474823828123</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1148007905305129</v>
+        <v>1.121857370280275</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.5712988496523688</v>
+        <v>0.5792277786976775</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.242533265324289</v>
+        <v>-0.5493123041876183</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.5576981665439147</v>
+        <v>0.945799739020485</v>
       </c>
     </row>
     <row r="6">
@@ -1456,178 +1456,178 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5147777398717445</v>
+        <v>-0.3767171684230672</v>
       </c>
       <c r="C6" t="n">
-        <v>1.836794920029707</v>
+        <v>-0.5318230314134172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06613218628048244</v>
+        <v>0.2313406382205673</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6473953044063089</v>
+        <v>-0.4396102209931603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4556313317785051</v>
+        <v>0.8948671640929639</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4607253483434048</v>
+        <v>-0.5820337025186726</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8286549733998811</v>
+        <v>-0.6483627064926745</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7650353305408972</v>
+        <v>0.1720554052236415</v>
       </c>
       <c r="J6" t="n">
-        <v>1.649853701557774</v>
+        <v>-0.7569560954488432</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5719959261367069</v>
+        <v>-0.502579963253739</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8171667290575987</v>
+        <v>-1.181642756916962</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7473993351321694</v>
+        <v>0.1421568669833512</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08329993314652087</v>
+        <v>1.591020162062742</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.08178067506352</v>
+        <v>-1.13419516051343</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3361598293655899</v>
+        <v>1.285124971868062</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5317120266874378</v>
+        <v>-0.3865730172863827</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2586656633880612</v>
+        <v>-0.4669956063693965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3572843755836221</v>
+        <v>0.06557166990701851</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3967415958358053</v>
+        <v>0.6554837734046167</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4112570857173658</v>
+        <v>0.3974308613088846</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5593789751831956</v>
+        <v>0.1271257095340492</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.9471298705158847</v>
+        <v>-0.8007846815868835</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3227123850424569</v>
+        <v>-0.8632201623429904</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2813167009031779</v>
+        <v>-0.04610245939596919</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.7826815179352299</v>
+        <v>-0.6098043513000677</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7025571559815386</v>
+        <v>-0.1001937930215374</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3738128496361892</v>
+        <v>-0.35103403646882</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.658092927417565</v>
+        <v>0.312382941573536</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.05791314033173477</v>
+        <v>-1.447851693947013</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2200436709457186</v>
+        <v>-0.4970512382204392</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5949687592051954</v>
+        <v>-0.4134058356962748</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.7273433844659404</v>
+        <v>-0.6962843086585333</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2490730345114039</v>
+        <v>0.3405760759082959</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.6229703767368931</v>
+        <v>0.9862463361761569</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.4049946679887789</v>
+        <v>1.334531933956778</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.6856742958158271</v>
+        <v>-0.5217151662484129</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2682903617781986</v>
+        <v>0.3464446614915459</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3629585458090488</v>
+        <v>1.045402552105455</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.7027665240608213</v>
+        <v>-0.712782619441461</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2299694416212617</v>
+        <v>1.090593436007328</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.6783527112101715</v>
+        <v>-0.6069407148488674</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.5665985212920824</v>
+        <v>-0.3692511110605302</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.5534170596638672</v>
+        <v>-0.6962142102936028</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.4727028131631187</v>
+        <v>0.7551656103680442</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.030361294787484</v>
+        <v>-0.6907005996435063</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.6719254828832779</v>
+        <v>-0.4425893393926291</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8087276405543525</v>
+        <v>-0.2168792483379262</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.5609458602436433</v>
+        <v>-0.3272082257009156</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3238337712605071</v>
+        <v>0.1239001142205732</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01871800364317401</v>
+        <v>1.093095983812614</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.665726669432769</v>
+        <v>0.2020639317646364</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.03874287828890667</v>
+        <v>0.5808144041909734</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.4768331448594383</v>
+        <v>0.9984452806657644</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.5322019573465337</v>
+        <v>-0.322342004900538</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1283252344548643</v>
+        <v>0.7177052383980841</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.02777467732189689</v>
+        <v>0.5578839631364128</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.5149525569999781</v>
+        <v>-0.3095446151735337</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.2076965051989599</v>
+        <v>0.6510029100554744</v>
       </c>
     </row>
     <row r="7">
@@ -1637,178 +1637,178 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3721302755765752</v>
+        <v>-0.6033175965753406</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02577911303293419</v>
+        <v>-0.6027703597916213</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1494982356421931</v>
+        <v>-0.1656934318000595</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4252469207497745</v>
+        <v>-0.6883467560882689</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9610100472194749</v>
+        <v>0.629281845920889</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6071856104804364</v>
+        <v>-0.01704763759827225</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6289683802886883</v>
+        <v>-0.8764177778085076</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2942468542996958</v>
+        <v>0.3343184981497263</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2448593223614249</v>
+        <v>-0.4187604768414681</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9537020469668864</v>
+        <v>0.01082009848689102</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7691835326248178</v>
+        <v>-0.04787602993507614</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1094823936947049</v>
+        <v>0.4264765828827268</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8465218574085177</v>
+        <v>0.3164737906097168</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.895355916555916</v>
+        <v>-0.3976087252570252</v>
       </c>
       <c r="P7" t="n">
-        <v>1.609533923334392</v>
+        <v>0.08755560316874367</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4078230752188634</v>
+        <v>-0.6232953591784143</v>
       </c>
       <c r="R7" t="n">
-        <v>1.03550380132187</v>
+        <v>0.6366176907705344</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07779343301545284</v>
+        <v>0.29270231444399</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6510202465731628</v>
+        <v>0.739402590309631</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6898620343573276</v>
+        <v>0.6151627638184501</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1226474648171319</v>
+        <v>0.1912097504247388</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7581864366192643</v>
+        <v>-0.9105109443674638</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3700146624016593</v>
+        <v>0.3399767009102412</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1101640873781128</v>
+        <v>-0.03792650415062983</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.5664070153382231</v>
+        <v>-0.8200012738057311</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.4893114030417661</v>
+        <v>0.04448898005834701</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.6532715657337624</v>
+        <v>-0.1470577953578388</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.9613991733646874</v>
+        <v>1.200693396783845</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1.010699129688553</v>
+        <v>0.1318419423406963</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.5772158172325632</v>
+        <v>-0.3202778928064836</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.4125573206773008</v>
+        <v>-0.6184033622805355</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.6044770884658013</v>
+        <v>-0.7613784178438543</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.2244368071728079</v>
+        <v>0.2473015090373202</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.8306050741893912</v>
+        <v>0.4263643641112522</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.141074364704312</v>
+        <v>0.3190541547627096</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.5166381715970847</v>
+        <v>-0.7438961171242532</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.3688435399443417</v>
+        <v>0.3082747170125293</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.7761508718797911</v>
+        <v>1.269189938796478</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.6455338823555025</v>
+        <v>-0.4648376954933589</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.017949479456794</v>
+        <v>0.2553684430360184</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.6916440356552996</v>
+        <v>-0.5605701518915972</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.365602101172981</v>
+        <v>-0.5990484866784366</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.5115554103852891</v>
+        <v>-0.5743477240554329</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.4525579158754168</v>
+        <v>0.4907550319903807</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.5075024616646415</v>
+        <v>1.185328160697487</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1639224930565581</v>
+        <v>-0.2945104648675377</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.1986978143891437</v>
+        <v>0.3111763170958706</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.2523060802004511</v>
+        <v>-0.5463360236871885</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.1759040819593401</v>
+        <v>0.3896580121886163</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.75662295533649</v>
+        <v>-0.9932780906453402</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3441287056344803</v>
+        <v>2.214738087719373</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.3126477483581722</v>
+        <v>-0.06165576702871595</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.529003210360274</v>
+        <v>0.6972354049459646</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.3320158952230872</v>
+        <v>-0.5588211107986305</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.3056159420104833</v>
+        <v>0.375128430238886</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.460058411994141</v>
+        <v>-0.1267481245799605</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.3131097119962803</v>
+        <v>-0.5403773488236021</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1164023577715763</v>
+        <v>0.1953054781853804</v>
       </c>
     </row>
     <row r="8">
@@ -1818,178 +1818,178 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.257196461926325</v>
+        <v>-0.0147214706176815</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.601612764164449</v>
+        <v>-0.7142293749936452</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2785522847531868</v>
+        <v>-0.3263987853698467</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.32749442074192</v>
+        <v>-0.03471433066772041</v>
       </c>
       <c r="F8" t="n">
-        <v>1.40522317474266</v>
+        <v>-1.010620979011355</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2074759871190683</v>
+        <v>1.216531250016758</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4881975689747889</v>
+        <v>0.4119307437118355</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1112431168192045</v>
+        <v>-0.7676827456106496</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5003967346659076</v>
+        <v>-0.7015363495059757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8720269683678079</v>
+        <v>0.342495542741411</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9732352919821886</v>
+        <v>0.8466186713042108</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1618915848400715</v>
+        <v>-0.5985557036959832</v>
       </c>
       <c r="N8" t="n">
-        <v>1.384355389420643</v>
+        <v>-0.51825973474966</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9466837371807788</v>
+        <v>1.474397466602823</v>
       </c>
       <c r="P8" t="n">
-        <v>1.23746189508221</v>
+        <v>-0.6103695929152998</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2998780095932745</v>
+        <v>-0.04027879692230027</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2289430745968061</v>
+        <v>0.2165544788170969</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3167935437926752</v>
+        <v>-0.1675363206620037</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08025276242275517</v>
+        <v>-0.6439773956568966</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6370200421918027</v>
+        <v>-0.1765546641431416</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2573339295629509</v>
+        <v>-0.3545277191035983</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6336466384131743</v>
+        <v>1.933164061449983</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4502889088450512</v>
+        <v>1.277728488301983</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.4342081142774654</v>
+        <v>-0.1926673298401581</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.4655064453749111</v>
+        <v>-0.03811757194877726</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.376521217081664</v>
+        <v>-0.3622003698899692</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.494814032443585</v>
+        <v>0.09149699525842599</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6561852310106777</v>
+        <v>-0.4460599750973828</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.370217016111442</v>
+        <v>0.6989008692005002</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.5473296123618798</v>
+        <v>0.9860524961938041</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.3002540687630012</v>
+        <v>-0.04898360557485983</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.5468227186748075</v>
+        <v>0.217002240991879</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.2695494270128139</v>
+        <v>-0.2738171606144324</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.9226030006535108</v>
+        <v>-0.4284328513418046</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.346444118960633</v>
+        <v>-0.9499597055913205</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.3996839545207619</v>
+        <v>0.4266580848524807</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.4080234028617756</v>
+        <v>-0.599478052590091</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27688874063683</v>
+        <v>-0.8053824302576243</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.2352733662544282</v>
+        <v>1.466659070070133</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.002744781160209</v>
+        <v>-0.3301694990024007</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.6863790526011416</v>
+        <v>1.76888610799729</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.2456076136670676</v>
+        <v>-0.02031393240589809</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.3986804491268344</v>
+        <v>1.753316529870202</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2710528251780309</v>
+        <v>-0.6341926773910642</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.4784900441536665</v>
+        <v>-0.8332084924927027</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.86931544207594</v>
+        <v>-0.04293245436686976</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.4432616118600276</v>
+        <v>-0.3129829408002778</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.2263626295497681</v>
+        <v>0.05714608918346994</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.3313649929799121</v>
+        <v>-0.04066726243752385</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.898927372531761</v>
+        <v>-0.07830655373006767</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.6347011210600971</v>
+        <v>0.3257425186362982</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.2763834319117308</v>
+        <v>0.3055655772823941</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.1817103931630246</v>
+        <v>-0.6709650804897127</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.2048179324991219</v>
+        <v>-0.003889864688466936</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.2348212412502682</v>
+        <v>-0.4139955567259871</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.4500314904248445</v>
+        <v>-0.3858796788736581</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1892904500619628</v>
+        <v>0.002088649132075854</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1408248411082247</v>
+        <v>-0.5861878969188045</v>
       </c>
     </row>
     <row r="9">
@@ -1999,178 +1999,178 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.07216194190175694</v>
+        <v>-0.2436204117334973</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7177064302543701</v>
+        <v>-0.4827822240661255</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3136918901382723</v>
+        <v>-0.3916713497756577</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09262180330114053</v>
+        <v>-0.2973392340820495</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9367831440410858</v>
+        <v>1.282399339754705</v>
       </c>
       <c r="G9" t="n">
-        <v>1.312494609971069</v>
+        <v>0.8452436081530722</v>
       </c>
       <c r="H9" t="n">
-        <v>0.398742336457018</v>
+        <v>-0.4511329485883623</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7447187892835131</v>
+        <v>0.06962706537725578</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7013911917340534</v>
+        <v>-0.156831100461688</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3167958792387403</v>
+        <v>-0.297091927144006</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6651742467870797</v>
+        <v>-0.4909485017879782</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5675486223425343</v>
+        <v>-0.1035747949695797</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5020832848539752</v>
+        <v>0.8738865863097626</v>
       </c>
       <c r="O9" t="n">
-        <v>1.370334443628034</v>
+        <v>-0.6046163813785013</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5123617110609645</v>
+        <v>1.358853099438885</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0952513289421241</v>
+        <v>-0.2947959620523572</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2300323753040453</v>
+        <v>1.173774773154932</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1316716091151597</v>
+        <v>-0.300052747764765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6272174926525055</v>
+        <v>-0.8905949920997368</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1516604995142141</v>
+        <v>0.7030824981567095</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3494787000447563</v>
+        <v>-0.148819169657309</v>
       </c>
       <c r="W9" t="n">
-        <v>2.089835792052309</v>
+        <v>-0.5837535456219021</v>
       </c>
       <c r="X9" t="n">
-        <v>1.34042948043308</v>
+        <v>-0.09738635861846213</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1735439862030951</v>
+        <v>-0.3940593535121683</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1135231598141143</v>
+        <v>-0.4349537073643138</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3152309735637168</v>
+        <v>0.1924986376466776</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1562081755965582</v>
+        <v>-0.2882471324375148</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4027821640004907</v>
+        <v>1.005381996427426</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.7521607142648242</v>
+        <v>-0.9463442779900354</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.005694727116117</v>
+        <v>-0.6297873978049743</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1075902714619781</v>
+        <v>-0.2859128730291537</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1890175949580065</v>
+        <v>-0.4799754133309231</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.2426813801850297</v>
+        <v>-0.4993494789880361</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.3722867352634027</v>
+        <v>0.7331852471996098</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.8796799123406135</v>
+        <v>1.037483870452765</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4264601937441495</v>
+        <v>-0.3782298599772944</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.558353935180349</v>
+        <v>-0.7375240229435194</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.7409602186766212</v>
+        <v>0.9677988723995117</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.54502265343312</v>
+        <v>-0.3308631208660429</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.4060254948740543</v>
+        <v>1.023857248139836</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.882151827802253</v>
+        <v>-0.6181956540352642</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.07906075087153137</v>
+        <v>-0.2337195952834396</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.869320504735005</v>
+        <v>-0.2664513737657125</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.6245959975960443</v>
+        <v>0.2134185345526218</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.8615860867211202</v>
+        <v>-0.4713690364915198</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.1982253575267151</v>
+        <v>-0.2701319970455631</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.2771443655295712</v>
+        <v>-0.4602850496882535</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.05217680186608082</v>
+        <v>-0.1968546281059648</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.2785525279299065</v>
+        <v>-0.436360228131848</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03564448552954929</v>
+        <v>1.334837593696428</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.3654841744886463</v>
+        <v>0.900076904534202</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.06776048288547536</v>
+        <v>-0.2121685741762238</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.665760118466009</v>
+        <v>0.1829572920453347</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.06401445171535974</v>
+        <v>-0.1995647881744463</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.3827765201814624</v>
+        <v>-0.6159239352456275</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.3868104928806335</v>
+        <v>-0.9310629483002705</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05642369247521681</v>
+        <v>-0.1816471407889169</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.5331283087673758</v>
+        <v>-0.2788173034825638</v>
       </c>
     </row>
     <row r="10">
@@ -2180,178 +2180,178 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3827168053781297</v>
+        <v>-0.3144051876645565</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.700721263898037</v>
+        <v>0.1646672390606629</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2119486431139226</v>
+        <v>-0.2339914859006063</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3262286312443887</v>
+        <v>-0.3842981410220482</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.43901055346424</v>
+        <v>1.305714132439312</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1423861520423502</v>
+        <v>-0.415343581325204</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2785668050716165</v>
+        <v>-0.5819051011503721</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6522645001269719</v>
+        <v>0.3312789332882262</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7310377871580087</v>
+        <v>0.1658268386263951</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.09053967077948254</v>
+        <v>1.406383914440177</v>
       </c>
       <c r="L10" t="n">
-        <v>2.766462459901299</v>
+        <v>-0.6981047038081023</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3787675156614981</v>
+        <v>0.2618344217449909</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3229677935850371</v>
+        <v>-0.4990332302298799</v>
       </c>
       <c r="O10" t="n">
-        <v>2.333655254067653</v>
+        <v>-0.8312122215345308</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.301853558930787</v>
+        <v>0.6304746957133046</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3225680445023232</v>
+        <v>-0.3556266186200951</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001852435693051413</v>
+        <v>0.8504461712724483</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0750841889861126</v>
+        <v>-0.0601559961219937</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5547979299582528</v>
+        <v>-0.1794839651989005</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003264569405436026</v>
+        <v>0.6235391937050258</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1473125239077196</v>
+        <v>-0.1394084617987622</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3952418939066989</v>
+        <v>-0.6856925943396627</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5139449396624983</v>
+        <v>0.1291701263376367</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3350656357770571</v>
+        <v>-0.4088387155333748</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3928740516645353</v>
+        <v>-0.511272441290867</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.9436662103614721</v>
+        <v>1.890660745245629</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.2563947036344725</v>
+        <v>1.067432998150927</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.684985575726528</v>
+        <v>0.8365783351620922</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.4458841076407286</v>
+        <v>-0.1061967300411094</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.058680518588659</v>
+        <v>-0.4728011066489913</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3236263654791435</v>
+        <v>-0.3656596086916599</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2749589355102356</v>
+        <v>-0.5165825061428685</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.05895401360508969</v>
+        <v>-0.1829331342174653</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.234784482305584</v>
+        <v>0.4716505996874045</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-1.470555750997705</v>
+        <v>0.4665197100494223</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3171369210587337</v>
+        <v>-0.4535357039188294</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.5761033107434673</v>
+        <v>-0.1308896176487061</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.9880337819528762</v>
+        <v>1.112938895255352</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.5450870776576017</v>
+        <v>-0.3219204329489079</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.3045884211054704</v>
+        <v>0.7627823492245943</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.4120882659599611</v>
+        <v>-0.5820569321433862</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.3485070277195005</v>
+        <v>-0.3226832147774396</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.7842300430453498</v>
+        <v>0.02081182152468492</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.4619764921381001</v>
+        <v>0.09119188546787811</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.4554466905908723</v>
+        <v>0.2822593961146943</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8243936141434667</v>
+        <v>-0.6781213826387875</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.09967808367698736</v>
+        <v>0.01148746330891403</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5855925295798947</v>
+        <v>-0.3837335859541059</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3243205171020808</v>
+        <v>-0.1400064684044985</v>
       </c>
       <c r="AY10" t="n">
-        <v>-1.123869170074933</v>
+        <v>0.2978612901253333</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.2012498753619407</v>
+        <v>-0.4797645730077068</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.3984226496075149</v>
+        <v>-0.475532801757493</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.51098240895576</v>
+        <v>0.1330527394513438</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.3845605207706443</v>
+        <v>-0.2722410950836285</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.2869953735950083</v>
+        <v>-0.1375114183534614</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.08480196511922235</v>
+        <v>-0.5955820206000071</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.3891155811851235</v>
+        <v>-0.2512311293694213</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.5058801767342505</v>
+        <v>-0.08830437899801391</v>
       </c>
     </row>
     <row r="11">
@@ -2361,178 +2361,178 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3156673364232819</v>
+        <v>0.3172548240136987</v>
       </c>
       <c r="C11" t="n">
-        <v>0.371188438618809</v>
+        <v>0.1638233414015755</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5327181348092468</v>
+        <v>-0.4857639320863117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2322760912332646</v>
+        <v>0.2336061531606672</v>
       </c>
       <c r="F11" t="n">
-        <v>1.007040578794042</v>
+        <v>0.8619585254149057</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2275505679895513</v>
+        <v>-0.1648961524310327</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02989091709047733</v>
+        <v>0.04149208939653959</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1759406059319011</v>
+        <v>-0.03095642563759634</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04572103834293417</v>
+        <v>0.008656069784877561</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3146325246637194</v>
+        <v>-0.1318831578734438</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7313915628628842</v>
+        <v>-0.9619941574088194</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1541393509271859</v>
+        <v>-0.2923229596771026</v>
       </c>
       <c r="N11" t="n">
-        <v>1.457073799944465</v>
+        <v>1.636249110891196</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7959548776063743</v>
+        <v>-1.008828244391222</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7963269410775891</v>
+        <v>0.6578378622962793</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2725368211736333</v>
+        <v>0.2787919275742971</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.3577006803750199</v>
+        <v>-0.9015216850628959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.458481405204764</v>
+        <v>-0.3967569360482173</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2292884148595466</v>
+        <v>0.3576753743827229</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.03255520910574104</v>
+        <v>-0.3451544323064771</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6164364379571475</v>
+        <v>-0.4784496430272744</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08902558742085016</v>
+        <v>-0.08161581901418645</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04006402943906121</v>
+        <v>-0.2143026242222578</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.069024284668823</v>
+        <v>-0.7678897104186068</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.09890370445745801</v>
+        <v>0.09965153774197609</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1482767674113328</v>
+        <v>0.5352829134933048</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.9777904139769894</v>
+        <v>-0.5278221390659166</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3074792281373923</v>
+        <v>0.04158039497788409</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.7038151668128585</v>
+        <v>-0.579277480037603</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.576283535156898</v>
+        <v>-1.136994805519233</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2525001480657401</v>
+        <v>0.2540329215964531</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004406693632155275</v>
+        <v>-0.00326080378937004</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.5503216454107334</v>
+        <v>-0.3744080799740797</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.04764418360986488</v>
+        <v>-0.2842650351033814</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.132456023532695</v>
+        <v>1.225823529057998</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1757181732481447</v>
+        <v>0.1739401110691435</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2079763978386725</v>
+        <v>0.2966181958151257</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.031344434485808</v>
+        <v>0.9361996983960365</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.9116282886182859</v>
+        <v>-0.7746242394896684</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.08605080062272114</v>
+        <v>-0.4902448043990135</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.5046429068709323</v>
+        <v>-0.5044887118797554</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.3364568497301312</v>
+        <v>0.3318712123273348</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.6967374645405128</v>
+        <v>-0.5746846915637641</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.03229135154029383</v>
+        <v>0.1672798921088584</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.05432286614231267</v>
+        <v>-0.116474657263713</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.6318460032767118</v>
+        <v>0.5480749402002715</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.8707432475313764</v>
+        <v>-0.4468098231986358</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.216764646343306</v>
+        <v>0.2069182292771127</v>
       </c>
       <c r="AX11" t="n">
-        <v>-1.157211699796924</v>
+        <v>-0.6553769475493459</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.6132331833779049</v>
+        <v>0.5509541494600224</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3769532952505576</v>
+        <v>0.2867454697099689</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0.09974978157074559</v>
+        <v>-0.2384606560801747</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.3859181515431905</v>
+        <v>0.07829418702110465</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4174366966103685</v>
+        <v>0.4029165195736338</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.5227323406620189</v>
+        <v>-0.3168195925900715</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.423151989800665</v>
+        <v>1.374545706557823</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.3964330590837828</v>
+        <v>0.396667699825255</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1211748966871131</v>
+        <v>0.2767499008955956</v>
       </c>
     </row>
     <row r="12">
@@ -2542,178 +2542,178 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1113544444049499</v>
+        <v>0.3910024056445046</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5063984662012025</v>
+        <v>-0.7011245823674613</v>
       </c>
       <c r="D12" t="n">
-        <v>1.521929459531798</v>
+        <v>-0.1773485917255863</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8958176991081976</v>
+        <v>0.3265974392955179</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9834616308396213</v>
+        <v>-1.476699556318596</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1703140249376178</v>
+        <v>0.05234156283254358</v>
       </c>
       <c r="H12" t="n">
-        <v>1.963339437326958</v>
+        <v>0.2648192519205655</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7472696911808439</v>
+        <v>-0.6297830663709736</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6606873062113837</v>
+        <v>-0.7480290527674911</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1733697526041747</v>
+        <v>-0.1604293784208924</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6250817710989648</v>
+        <v>2.93950870064869</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2624281234709149</v>
+        <v>-0.321477086995176</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5871122605938456</v>
+        <v>-0.3162449035340934</v>
       </c>
       <c r="O12" t="n">
-        <v>1.091995089481907</v>
+        <v>2.400170612909273</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8281975125628247</v>
+        <v>-1.304849127099966</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02183495590953862</v>
+        <v>0.3269900579830445</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2397752885865806</v>
+        <v>0.02034519839974019</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08659537106555353</v>
+        <v>0.1750475206965112</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03535407505627783</v>
+        <v>-0.5527842820635661</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4117566453017566</v>
+        <v>0.06814565467409235</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1199549201332492</v>
+        <v>0.2496744848414965</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5802077258006776</v>
+        <v>0.3390273181930249</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4307569409091829</v>
+        <v>0.470146230218113</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5214837597510155</v>
+        <v>0.4791119955471251</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.1069170061708281</v>
+        <v>0.4858158195278837</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.6026896997984416</v>
+        <v>-1.024036953023809</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.5392610263812476</v>
+        <v>-0.2317715213898452</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2565950254065457</v>
+        <v>-0.6974706989894697</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.04161809032986995</v>
+        <v>0.509634593309538</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7401493859456498</v>
+        <v>1.129404757350203</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.3124805814497351</v>
+        <v>0.3264104296125312</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.1330663238286638</v>
+        <v>0.3115011387294625</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.04871536423844226</v>
+        <v>0.02383666485582368</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.4885869598195818</v>
+        <v>-0.1288887075599716</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.9339003960289389</v>
+        <v>-1.532305684584013</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.4000917244397824</v>
+        <v>0.3320543585972964</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.152011792906722</v>
+        <v>-0.5507387420976086</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.8987804514905888</v>
+        <v>-0.9826846980133315</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.939040997376298</v>
+        <v>0.4952965341526941</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5451828376337918</v>
+        <v>0.3410594151494035</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6968383381206612</v>
+        <v>0.3284662288195032</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.2705861916252651</v>
+        <v>0.3525928327464163</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.4608316742794427</v>
+        <v>0.7975019684342743</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.4259061974466188</v>
+        <v>-0.4477312667405549</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0.6734760011777953</v>
+        <v>-0.4676767310500131</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.1595043095792393</v>
+        <v>0.8312685364109142</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.3532011862695705</v>
+        <v>-0.01500095914433181</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.12848572318549</v>
+        <v>0.5715637715986898</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.1287603451606383</v>
+        <v>0.03259326698658409</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.5451075379147692</v>
+        <v>-1.146014472470452</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.2765559580135561</v>
+        <v>-0.3124617127162213</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.1971560804372985</v>
+        <v>-0.1369221798656295</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.3920182391746538</v>
+        <v>-0.4986871631921065</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.1098052638803748</v>
+        <v>0.3885416946287147</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.5298250203659371</v>
+        <v>-0.2276879531399851</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.1887756970199179</v>
+        <v>-0.05568680028976067</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1058492367056292</v>
+        <v>0.3945968138682525</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3161192531584488</v>
+        <v>-0.4515289420316964</v>
       </c>
     </row>
     <row r="13">
@@ -2723,178 +2723,178 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3654026778739324</v>
+        <v>-0.08774136601516197</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3520954106755199</v>
+        <v>-0.5921591766897193</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3869490716533264</v>
+        <v>1.51369879101545</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4578347027508535</v>
+        <v>0.967560034771749</v>
       </c>
       <c r="F13" t="n">
-        <v>1.191064428777074</v>
+        <v>-1.020455936850551</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4490066864497678</v>
+        <v>0.1895534814013086</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6561131340311308</v>
+        <v>2.023205737541201</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8325650059743819</v>
+        <v>-0.7924546984182933</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4575545064049725</v>
+        <v>-0.7347765854789334</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1060837189836819</v>
+        <v>-0.1237117879901226</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.106194651374639</v>
+        <v>0.701294428947789</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07066477830500359</v>
+        <v>-0.2962559547636288</v>
       </c>
       <c r="N13" t="n">
-        <v>1.242033983856323</v>
+        <v>-0.6276335047796915</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.519943401808234</v>
+        <v>1.147809709641505</v>
       </c>
       <c r="P13" t="n">
-        <v>0.666168516643036</v>
+        <v>-0.8898442824553756</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3505725539390411</v>
+        <v>0.04594307991151144</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.8353586693513347</v>
+        <v>0.2357581052680019</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3405506057488519</v>
+        <v>-0.09468244081382646</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4633257910785063</v>
+        <v>0.02613594119699223</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3882675050695997</v>
+        <v>-0.4268154023740093</v>
       </c>
       <c r="V13" t="n">
-        <v>0.454032413352381</v>
+        <v>-0.1494417058285339</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.8168997674794289</v>
+        <v>0.6496220051285028</v>
       </c>
       <c r="X13" t="n">
-        <v>0.008290994518498351</v>
+        <v>0.4956961100581638</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4870903543018971</v>
+        <v>0.5054376152224553</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.6002591691049352</v>
+        <v>-0.0687098636959958</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5016781862967363</v>
+        <v>-0.5858329816504624</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01547221298183489</v>
+        <v>0.5772882859221073</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.6725229774662216</v>
+        <v>-0.2693449438965698</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.8816987045816423</v>
+        <v>0.0886244753148195</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02119425930413672</v>
+        <v>0.7725252679767238</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.3784995938504208</v>
+        <v>0.3399320688571335</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.4774454652807789</v>
+        <v>-0.0922391091690533</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.2988926926186294</v>
+        <v>0.03979091623022947</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.381796554188494</v>
+        <v>-0.5288263537409996</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.9915055375822285</v>
+        <v>-0.9893901803505438</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.5125050165603287</v>
+        <v>0.4495331982880638</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.427291450495984</v>
+        <v>-0.1574026600541479</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.8045775501598387</v>
+        <v>-0.9210873523225482</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.5244653447221882</v>
+        <v>1.955904140823279</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.7417872267950696</v>
+        <v>0.5483052267456388</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.6927052769307335</v>
+        <v>0.7547592088080399</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.3335563998614042</v>
+        <v>0.2931521923572706</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.2058580814107568</v>
+        <v>0.5278212931280148</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.6700214354649291</v>
+        <v>-0.4560687292997012</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.01026442726674737</v>
+        <v>-0.6925927249038974</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.01812703296310042</v>
+        <v>-0.1551336989599658</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.5759334517988774</v>
+        <v>-0.379612127809348</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.4047264114645118</v>
+        <v>-0.1115559419152408</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.7948615747041402</v>
+        <v>-0.1369871360681688</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.4954973695947466</v>
+        <v>-0.6115908790652421</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.3944704052901681</v>
+        <v>-0.2862528423151773</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.2544790141078035</v>
+        <v>0.1946063777202419</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.5351464930185242</v>
+        <v>-0.435891765880381</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.310906916795261</v>
+        <v>-0.08683824007282116</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.4762098378895959</v>
+        <v>0.5214596571107225</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.3742597995538794</v>
+        <v>-0.1747547639164133</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.2845030670939122</v>
+        <v>-0.08318988928920489</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.378115446920299</v>
+        <v>-0.3303760156434544</v>
       </c>
     </row>
     <row r="14">
@@ -2904,178 +2904,178 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05226907015582238</v>
+        <v>0.02857358882996676</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.6009101957477572</v>
+        <v>-0.5938958158572921</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2300838078012798</v>
+        <v>-0.214687977401147</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06529021138754702</v>
+        <v>0.03373098003675933</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.264299785044095</v>
+        <v>-1.214406471460216</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1349909096415705</v>
+        <v>0.1399155108539692</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04042211303039508</v>
+        <v>0.01784278297236095</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6966520091462092</v>
+        <v>-0.6735995574956293</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5899263391426074</v>
+        <v>-0.5821338628966194</v>
       </c>
       <c r="K14" t="n">
-        <v>1.401972386120763</v>
+        <v>1.427554196027148</v>
       </c>
       <c r="L14" t="n">
-        <v>1.529190200366426</v>
+        <v>1.455550373487511</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4867330418723</v>
+        <v>-0.4721789902672088</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2054800766244115</v>
+        <v>-0.2382926734704532</v>
       </c>
       <c r="O14" t="n">
-        <v>1.656390678828827</v>
+        <v>1.586931469130139</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.129743189690287</v>
+        <v>-1.096058165891199</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02299635469233778</v>
+        <v>0.0004642708177706563</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1762334427375226</v>
+        <v>0.1590258934398765</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.01718326309090557</v>
+        <v>-0.02164934471977934</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5153258357914555</v>
+        <v>-0.512543989997584</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05277778119609746</v>
+        <v>0.05923517244281082</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02118819814493798</v>
+        <v>0.01355952052534739</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1821845902989587</v>
+        <v>0.1617594329790635</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2216553274511899</v>
+        <v>0.2033581319659921</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1880012753628969</v>
+        <v>0.1685987932863742</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.699415788835891</v>
+        <v>3.765277405280547</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.8461583587242535</v>
+        <v>-0.8107517785822927</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2542100257417397</v>
+        <v>-0.2470134103789284</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.6560528262673817</v>
+        <v>-0.6338691643856791</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.03286817875550705</v>
+        <v>-0.0109758559172092</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6547887872484293</v>
+        <v>0.6164969457827928</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03130874872005737</v>
+        <v>-0.003038517226226857</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.92928877033468</v>
+        <v>2.999122126349725</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.06001627208357976</v>
+        <v>-0.05512271017060424</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.08558289462292065</v>
+        <v>0.0879163726414281</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-1.257031712275421</v>
+        <v>-1.226216117604528</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.1412744042949788</v>
+        <v>0.1121589806070996</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.4789154440597942</v>
+        <v>-0.4517585651075673</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.7665765842718993</v>
+        <v>-0.7293534125374003</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.2677843231612776</v>
+        <v>0.236586539622448</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.1757426630764317</v>
+        <v>-0.1765723443711067</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.08438724165457802</v>
+        <v>0.06932770252733898</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0280134019642761</v>
+        <v>0.004835978923883242</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.5556782753630721</v>
+        <v>0.5040782027525377</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0.4244153169795713</v>
+        <v>-0.4041100637814872</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.2794531168553068</v>
+        <v>-0.2576873148607302</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.543644325487857</v>
+        <v>0.4795178137290975</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.2064890648937223</v>
+        <v>-0.2031061698350672</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1447542726936334</v>
+        <v>0.1162450981950762</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.2123178097889848</v>
+        <v>-0.2050930731504686</v>
       </c>
       <c r="AY14" t="n">
-        <v>-1.028569903782678</v>
+        <v>-0.9909133133991601</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0.3743581832707741</v>
+        <v>-0.3453689631003481</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.2151495316908607</v>
+        <v>-0.1820358953857316</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.39297968825241</v>
+        <v>-0.3728216949749765</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.05262196970426168</v>
+        <v>0.02950757807333135</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.2859980879624601</v>
+        <v>-0.2682918295677559</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.3153848000703282</v>
+        <v>-0.2826777683943379</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.05776867158401208</v>
+        <v>0.03434179776316527</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.4975401458462634</v>
+        <v>-0.4581538458160249</v>
       </c>
     </row>
     <row r="15">
@@ -3085,178 +3085,178 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1277146419937461</v>
+        <v>-0.4391306710098853</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.8328122460652875</v>
+        <v>-0.2608603006166458</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2618335783241386</v>
+        <v>-0.4729770778549844</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1960987095070804</v>
+        <v>-0.5305733354912556</v>
       </c>
       <c r="F15" t="n">
-        <v>1.662392713820718</v>
+        <v>1.226885498044361</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.04041082466382698</v>
+        <v>-0.3206574854001482</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3620692128703039</v>
+        <v>-0.7339408108951194</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4700040054143875</v>
+        <v>0.8322387995363321</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.207160754847607</v>
+        <v>-0.2438286087157723</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6529398322417213</v>
+        <v>0.1661762000387388</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1468402837002077</v>
+        <v>-1.100320080682116</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2639904551772346</v>
+        <v>0.05837944396769326</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9975910876267877</v>
+        <v>1.240689282693828</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.004517875411416157</v>
+        <v>-1.54760537695232</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4787839148441934</v>
+        <v>0.8433792663659876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1871432274551834</v>
+        <v>-0.4335583481310846</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13392542860335</v>
+        <v>-0.6393425378152029</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1313084859404265</v>
+        <v>0.2830959984532536</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6006812247709139</v>
+        <v>0.4235191874486154</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3726759092011081</v>
+        <v>0.5156867270587343</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3538174676496144</v>
+        <v>0.4415441228560302</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4702742030074784</v>
+        <v>-0.8979024780630447</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4939867240911768</v>
+        <v>-0.08261821011212012</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.6333036169799167</v>
+        <v>0.4124734323263167</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3199516287555074</v>
+        <v>-0.671605163345851</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.283674374488068</v>
+        <v>0.6700015503921563</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4959235024626371</v>
+        <v>0.06138686847007772</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1861018654422962</v>
+        <v>0.8797457563651945</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4562966248985817</v>
+        <v>0.8816035465965676</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.6674651945601854</v>
+        <v>-0.01976292880746217</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1910003237952689</v>
+        <v>-0.4383943120458855</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.3195479398738475</v>
+        <v>-0.5448750539373823</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.30720084646741</v>
+        <v>0.2630310768421382</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.03580549271882856</v>
+        <v>0.6276186817280286</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.2210308320051985</v>
+        <v>1.103751391851629</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.2719101679585433</v>
+        <v>-0.5834978872948494</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.263259023545491</v>
+        <v>0.2901357171153298</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.910321012845059</v>
+        <v>0.7589880578957811</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.2616266335196105</v>
+        <v>-0.4256820224703151</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.404319848796159</v>
+        <v>-0.6046687421031403</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.2743535215376248</v>
+        <v>-0.7400946275612891</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.1370319199354888</v>
+        <v>-0.4067321009969772</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.5894129558386266</v>
+        <v>-0.2270916744104633</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.150277911734225</v>
+        <v>0.6629381832245753</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.4907736570637842</v>
+        <v>0.05507018462256281</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2407244430795134</v>
+        <v>-0.2590429486686185</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.4662786985171799</v>
+        <v>0.6398873162732555</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.2420077689066625</v>
+        <v>-0.313955997890199</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.3323753467975349</v>
+        <v>0.7357840639301879</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.5536819967548483</v>
+        <v>0.6481806808231347</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2663893327273718</v>
+        <v>-0.5972011540920213</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.4155788291392749</v>
+        <v>-0.2732653028928416</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.3509839022589343</v>
+        <v>0.4776160208775131</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0.08664710834241185</v>
+        <v>-0.3829217900608693</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.2068402856027648</v>
+        <v>0.2678352320086153</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.6236559923302579</v>
+        <v>0.07364011661418915</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.05929599995136968</v>
+        <v>-0.3590921244096008</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.06482546506137241</v>
+        <v>0.2185540969863019</v>
       </c>
     </row>
     <row r="16">
@@ -3266,178 +3266,178 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8558948446146875</v>
+        <v>0.9788289751742192</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5264072260248129</v>
+        <v>-0.5746715700003358</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4968823294545345</v>
+        <v>0.5577864822453926</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4846411374154659</v>
+        <v>0.5720628072095711</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6090393096026983</v>
+        <v>-0.7184313271702648</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4433521000164162</v>
+        <v>-0.4243828798872271</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0914228361332102</v>
+        <v>0.1552983368775506</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4042748333301881</v>
+        <v>0.416861936045497</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6229971096803801</v>
+        <v>-0.6668189670621718</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3628924382236918</v>
+        <v>0.4210510137922794</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4345252014782757</v>
+        <v>-0.4617961939638761</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3227943179117483</v>
+        <v>0.3263448216132314</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4388244161600222</v>
+        <v>-0.4603931659296491</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4922678135955332</v>
+        <v>-0.4928215955396966</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5713531266101567</v>
+        <v>-0.6222868265471991</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.268681088763071</v>
+        <v>1.413114965168387</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.633994644678977</v>
+        <v>-0.6940177004899055</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7734729023967395</v>
+        <v>0.8393552594675628</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.002768878847104905</v>
+        <v>-0.05624829372728005</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0753191237865964</v>
+        <v>0.0477644555444764</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5524093764117317</v>
+        <v>0.6038924017514027</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.420204913389271</v>
+        <v>-0.3644275775514998</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.008514688792386123</v>
+        <v>-0.03445601680083468</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4148806018255913</v>
+        <v>0.4673988249927141</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.2946565928276998</v>
+        <v>-0.2701004464598795</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.204655206438028</v>
+        <v>0.2509363823882581</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9775623933697726</v>
+        <v>1.104167464006256</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.5036127837131471</v>
+        <v>-0.5868353070836552</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.4398017773537339</v>
+        <v>0.4630702862709561</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.4190652969619028</v>
+        <v>0.4901221637734945</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.7339430212162881</v>
+        <v>0.7890981527504263</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04942866367570651</v>
+        <v>0.1077750200766753</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.7718620599077121</v>
+        <v>0.7836992959533461</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.3383859011559611</v>
+        <v>-0.3769468729512243</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.5537554399176756</v>
+        <v>-0.6196615596441759</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.677212160090868</v>
+        <v>0.7832746616739361</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.6489871849648771</v>
+        <v>0.7180620962571612</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.845697431329052</v>
+        <v>-0.9933550345404695</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.1484718919369624</v>
+        <v>-0.2527523433324249</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.4764884838095483</v>
+        <v>-0.5218219545797715</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.1040521217054404</v>
+        <v>-0.08078846018863736</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.4502420794246823</v>
+        <v>0.5296571192411169</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.1800266843239122</v>
+        <v>-0.1432450746774755</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.1322359110069458</v>
+        <v>0.1410057225422779</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0.6283222066678553</v>
+        <v>-0.7769585553339751</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.3540167671248438</v>
+        <v>-0.3710939603700864</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.3831359041130488</v>
+        <v>0.3870115760584737</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.9892825080339566</v>
+        <v>0.6762372098073074</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.3337694169319314</v>
+        <v>0.2454497444067966</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.8328463940901767</v>
+        <v>-0.8145741097027851</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0.6487896129275246</v>
+        <v>-0.7127163321347977</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.2876448929926063</v>
+        <v>0.3017752895118475</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.6288200029826646</v>
+        <v>-0.691130688768663</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.3053947228621495</v>
+        <v>0.3706565865189979</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.255405190150901</v>
+        <v>0.2675853242257519</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.4301865378835777</v>
+        <v>0.465603972967745</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.05380368339726691</v>
+        <v>0.09844219199296635</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.349622984772317</v>
+        <v>0.3792342356261509</v>
       </c>
     </row>
   </sheetData>
